--- a/dongle/results-22042026-105214.xlsx
+++ b/dongle/results-22042026-105214.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,100 +570,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>packet_loss_percent</t>
+          <t>total_packets</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.692307692307693</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>total_packets</t>
+          <t>lost_packets</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lost_packets</t>
+          <t>lost_percent</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lost_percent</t>
+          <t>cpu_host_total</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.692307692307693</v>
+        <v>0.4264391060190806</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cpu_host_total</t>
+          <t>cpu_host_user</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4264391060190806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cpu_host_user</t>
+          <t>cpu_host_system</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.4263699494593982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cpu_host_system</t>
+          <t>cpu_remote_total</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4263699494593982</v>
+        <v>0.1503282927361504</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cpu_remote_total</t>
+          <t>cpu_remote_user</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1503282927361504</v>
+        <v>0.00563494230716679</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cpu_remote_user</t>
+          <t>cpu_remote_system</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.00563494230716679</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cpu_remote_system</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
         <v>0.1447232704766323</v>
       </c>
     </row>
